--- a/Output/PowerPoint_Figures/Fig_7/Fig_7g_data.xlsx
+++ b/Output/PowerPoint_Figures/Fig_7/Fig_7g_data.xlsx
@@ -21,16 +21,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -41,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -49,21 +46,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -433,32 +421,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>FPR</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TPR</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TPR_Lower</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>TPR_Upper</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>AUC</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -482,7 +470,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -504,7 +492,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -526,7 +514,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -548,7 +536,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -570,7 +558,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -592,7 +580,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -614,7 +602,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -636,7 +624,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -658,7 +646,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -680,7 +668,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -702,7 +690,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -724,7 +712,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -746,7 +734,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -768,7 +756,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -790,7 +778,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -812,7 +800,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -834,7 +822,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -856,7 +844,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -878,7 +866,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -900,7 +888,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -922,7 +910,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -944,7 +932,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -966,7 +954,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -988,7 +976,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -1010,7 +998,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -1032,7 +1020,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1042,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1064,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -1098,7 +1086,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1108,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1130,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -1164,7 +1152,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1174,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1196,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1218,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1240,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1262,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -1296,7 +1284,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1306,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1328,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -1362,7 +1350,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1372,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1394,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1416,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -1450,7 +1438,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1460,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1482,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1504,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1526,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1548,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -1582,7 +1570,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1592,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -1626,7 +1614,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -1648,7 +1636,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1658,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -1692,7 +1680,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1702,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1724,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1746,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1768,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1790,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -1824,7 +1812,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -1846,7 +1834,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1856,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1878,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1900,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -1934,7 +1922,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -1956,7 +1944,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1966,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -2000,7 +1988,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2010,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -2044,7 +2032,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2054,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2076,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2098,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2120,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2142,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2164,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2186,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2208,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -2242,7 +2230,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2252,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2274,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -2308,7 +2296,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2318,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -2352,7 +2340,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -2374,7 +2362,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2384,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -2418,7 +2406,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2428,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2450,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2472,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2494,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -2528,7 +2516,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -2550,7 +2538,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2560,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -2594,7 +2582,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -2616,7 +2604,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2626,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2648,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -2679,32 +2667,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>FPR</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TPR</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TPR_Lower</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>TPR_Upper</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>AUC</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -2728,7 +2716,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -2750,7 +2738,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -2772,7 +2760,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -2794,7 +2782,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2804,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -2838,7 +2826,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2848,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -2882,7 +2870,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2892,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2914,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -2948,7 +2936,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -2970,7 +2958,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -2992,7 +2980,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -3014,7 +3002,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3024,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3046,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -3080,7 +3068,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -3102,7 +3090,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -3124,7 +3112,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3134,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3156,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -3190,7 +3178,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -3212,7 +3200,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -3234,7 +3222,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -3256,7 +3244,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3266,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3288,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -3322,7 +3310,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -3344,7 +3332,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3354,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -3388,7 +3376,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -3410,7 +3398,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3420,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -3454,7 +3442,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3464,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -3498,7 +3486,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -3520,7 +3508,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -3542,7 +3530,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -3564,7 +3552,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -3586,7 +3574,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -3608,7 +3596,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -3630,7 +3618,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -3652,7 +3640,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3662,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -3696,7 +3684,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -3718,7 +3706,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -3740,7 +3728,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -3762,7 +3750,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -3784,7 +3772,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -3806,7 +3794,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -3828,7 +3816,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -3850,7 +3838,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -3872,7 +3860,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3882,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -3916,7 +3904,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -3938,7 +3926,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -3960,7 +3948,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3970,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -4004,7 +3992,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -4026,7 +4014,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4036,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -4070,7 +4058,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4080,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -4114,7 +4102,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4124,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -4158,7 +4146,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4168,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -4202,7 +4190,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -4224,7 +4212,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -4246,7 +4234,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -4268,7 +4256,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -4290,7 +4278,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -4312,7 +4300,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4322,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4344,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -4378,7 +4366,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -4400,7 +4388,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -4422,7 +4410,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -4444,7 +4432,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -4466,7 +4454,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -4488,7 +4476,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -4510,7 +4498,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -4532,7 +4520,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -4554,7 +4542,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -4576,7 +4564,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4586,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -4620,7 +4608,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -4642,7 +4630,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -4664,7 +4652,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -4686,7 +4674,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -4708,7 +4696,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -4730,7 +4718,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -4752,7 +4740,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -4774,7 +4762,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -4796,7 +4784,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4806,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -4840,7 +4828,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -4862,7 +4850,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -4884,7 +4872,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -4906,7 +4894,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -4925,32 +4913,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>FPR</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TPR</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TPR_Lower</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>TPR_Upper</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>AUC</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -4974,7 +4962,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -4996,7 +4984,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -5018,7 +5006,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -5040,7 +5028,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5050,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -5084,7 +5072,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -5106,7 +5094,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -5128,7 +5116,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -5150,7 +5138,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -5172,7 +5160,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -5194,7 +5182,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -5216,7 +5204,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5226,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -5260,7 +5248,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -5282,7 +5270,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -5304,7 +5292,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5314,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5336,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -5370,7 +5358,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -5392,7 +5380,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -5414,7 +5402,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -5436,7 +5424,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -5458,7 +5446,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -5480,7 +5468,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -5502,7 +5490,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5512,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -5546,7 +5534,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -5568,7 +5556,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -5590,7 +5578,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -5612,7 +5600,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5622,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5644,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -5678,7 +5666,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -5700,7 +5688,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -5722,7 +5710,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -5744,7 +5732,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -5766,7 +5754,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -5788,7 +5776,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -5810,7 +5798,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -5832,7 +5820,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -5854,7 +5842,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -5876,7 +5864,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -5898,7 +5886,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -5920,7 +5908,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5930,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5952,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -5986,7 +5974,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -6008,7 +5996,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -6030,7 +6018,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -6052,7 +6040,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -6074,7 +6062,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -6096,7 +6084,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -6118,7 +6106,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -6140,7 +6128,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -6162,7 +6150,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -6184,7 +6172,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -6206,7 +6194,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -6228,7 +6216,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -6250,7 +6238,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -6272,7 +6260,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6282,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -6316,7 +6304,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6326,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6348,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -6382,7 +6370,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -6404,7 +6392,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -6426,7 +6414,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -6448,7 +6436,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6458,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -6492,7 +6480,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -6514,7 +6502,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -6536,7 +6524,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -6558,7 +6546,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -6580,7 +6568,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -6602,7 +6590,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -6624,7 +6612,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -6646,7 +6634,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6656,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -6690,7 +6678,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -6712,7 +6700,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -6734,7 +6722,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -6756,7 +6744,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -6778,7 +6766,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -6800,7 +6788,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -6822,7 +6810,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -6844,7 +6832,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -6866,7 +6854,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -6888,7 +6876,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -6910,7 +6898,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -6932,7 +6920,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -6954,7 +6942,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -6976,7 +6964,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -6998,7 +6986,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7008,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -7042,7 +7030,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -7064,7 +7052,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -7086,7 +7074,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -7108,7 +7096,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -7130,7 +7118,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -7152,7 +7140,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -7171,32 +7159,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>FPR</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TPR</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TPR_Lower</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>TPR_Upper</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>AUC</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -7220,7 +7208,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -7242,7 +7230,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -7264,7 +7252,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -7286,7 +7274,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -7308,7 +7296,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -7330,7 +7318,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -7352,7 +7340,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -7374,7 +7362,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -7396,7 +7384,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -7418,7 +7406,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -7440,7 +7428,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -7462,7 +7450,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -7484,7 +7472,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -7506,7 +7494,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -7528,7 +7516,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -7550,7 +7538,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -7572,7 +7560,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7582,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -7616,7 +7604,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -7638,7 +7626,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -7660,7 +7648,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -7682,7 +7670,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -7704,7 +7692,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -7726,7 +7714,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -7748,7 +7736,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -7770,7 +7758,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -7792,7 +7780,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -7814,7 +7802,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -7836,7 +7824,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -7858,7 +7846,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -7880,7 +7868,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7890,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -7924,7 +7912,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -7946,7 +7934,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -7968,7 +7956,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -7990,7 +7978,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -8012,7 +8000,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -8034,7 +8022,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -8056,7 +8044,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -8078,7 +8066,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -8100,7 +8088,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -8122,7 +8110,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -8144,7 +8132,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -8166,7 +8154,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -8188,7 +8176,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -8210,7 +8198,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -8232,7 +8220,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -8254,7 +8242,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -8276,7 +8264,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -8298,7 +8286,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -8320,7 +8308,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -8342,7 +8330,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -8364,7 +8352,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8374,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -8408,7 +8396,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -8430,7 +8418,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -8452,7 +8440,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -8474,7 +8462,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -8496,7 +8484,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -8518,7 +8506,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -8540,7 +8528,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -8562,7 +8550,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -8584,7 +8572,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -8606,7 +8594,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -8628,7 +8616,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -8650,7 +8638,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -8672,7 +8660,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -8694,7 +8682,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -8716,7 +8704,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -8738,7 +8726,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -8760,7 +8748,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -8782,7 +8770,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -8804,7 +8792,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -8826,7 +8814,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -8848,7 +8836,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -8870,7 +8858,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -8892,7 +8880,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -8914,7 +8902,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -8936,7 +8924,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -8958,7 +8946,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8968,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -9002,7 +8990,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -9024,7 +9012,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -9046,7 +9034,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -9068,7 +9056,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -9090,7 +9078,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -9112,7 +9100,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9122,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -9156,7 +9144,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -9178,7 +9166,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -9200,7 +9188,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -9222,7 +9210,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -9244,7 +9232,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -9266,7 +9254,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -9288,7 +9276,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -9310,7 +9298,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -9332,7 +9320,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -9354,7 +9342,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -9376,7 +9364,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -9398,7 +9386,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -9417,32 +9405,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>FPR</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TPR</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TPR_Lower</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>TPR_Upper</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>AUC</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -9466,7 +9454,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -9488,7 +9476,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -9510,7 +9498,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -9532,7 +9520,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9542,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9564,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -9598,7 +9586,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -9620,7 +9608,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -9642,7 +9630,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -9664,7 +9652,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -9686,7 +9674,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -9708,7 +9696,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -9730,7 +9718,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -9752,7 +9740,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -9774,7 +9762,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -9796,7 +9784,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -9818,7 +9806,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -9840,7 +9828,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9850,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -9884,7 +9872,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -9906,7 +9894,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -9928,7 +9916,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -9950,7 +9938,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -9972,7 +9960,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -9994,7 +9982,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -10016,7 +10004,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -10038,7 +10026,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -10060,7 +10048,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -10082,7 +10070,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -10104,7 +10092,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -10126,7 +10114,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -10148,7 +10136,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -10170,7 +10158,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -10192,7 +10180,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -10214,7 +10202,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -10236,7 +10224,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -10258,7 +10246,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -10280,7 +10268,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -10302,7 +10290,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -10324,7 +10312,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -10346,7 +10334,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -10368,7 +10356,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -10390,7 +10378,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -10412,7 +10400,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -10434,7 +10422,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -10456,7 +10444,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -10478,7 +10466,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -10500,7 +10488,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -10522,7 +10510,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -10544,7 +10532,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -10566,7 +10554,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -10588,7 +10576,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -10610,7 +10598,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -10632,7 +10620,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -10654,7 +10642,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -10676,7 +10664,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -10698,7 +10686,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -10720,7 +10708,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -10742,7 +10730,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -10764,7 +10752,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -10786,7 +10774,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -10808,7 +10796,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -10830,7 +10818,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -10852,7 +10840,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -10874,7 +10862,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -10896,7 +10884,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -10918,7 +10906,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10928,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -10962,7 +10950,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -10984,7 +10972,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -11006,7 +10994,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -11028,7 +11016,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -11050,7 +11038,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -11072,7 +11060,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11082,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -11116,7 +11104,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -11138,7 +11126,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -11160,7 +11148,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -11182,7 +11170,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -11204,7 +11192,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -11226,7 +11214,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -11248,7 +11236,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -11270,7 +11258,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -11292,7 +11280,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -11314,7 +11302,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -11336,7 +11324,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -11358,7 +11346,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -11380,7 +11368,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -11402,7 +11390,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -11424,7 +11412,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11434,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -11468,7 +11456,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -11490,7 +11478,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -11512,7 +11500,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -11534,7 +11522,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -11556,7 +11544,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -11578,7 +11566,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -11600,7 +11588,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -11622,7 +11610,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
@@ -11644,7 +11632,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\ADMET_Comparison\roc_curves_admet.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/ADMET_Comparison/roc_curves_admet.xlsx</t>
         </is>
       </c>
     </row>
